--- a/database/huong dan IssueInOut.xlsx
+++ b/database/huong dan IssueInOut.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70K6885\Desktop\back up job 04012026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desktops\code suport 2020\Dao\June.2022_MaterialTranfer\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A74984-C0AB-4BE2-B9E0-AB97713503B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CC69B6-0F4C-4447-9D63-60AC8AF07DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7595A650-7345-43C4-BEA2-9DD7FDDC8FC4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,16 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>bo phan phe duyet</t>
-  </si>
-  <si>
-    <t>ke toan phe duyet</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Riêng phòng PUR thì update phần lưu kho là những người làm RQ sau khi kế toán approved thành công(OK)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -106,6 +97,30 @@
   </si>
   <si>
     <t>Truong hop Out stock</t>
+  </si>
+  <si>
+    <t>1. Fom đăng nhập</t>
+  </si>
+  <si>
+    <t>2.bo phan phe duyet</t>
+  </si>
+  <si>
+    <t>Level 1</t>
+  </si>
+  <si>
+    <t>level 2</t>
+  </si>
+  <si>
+    <t>level 3</t>
+  </si>
+  <si>
+    <t>kế toán phê duyệt</t>
+  </si>
+  <si>
+    <t>level 1</t>
+  </si>
+  <si>
+    <t>Level 2</t>
   </si>
 </sst>
 </file>
@@ -183,15 +198,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>598714</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>157842</xdr:rowOff>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>130627</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>375603</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>101781</xdr:rowOff>
+      <xdr:colOff>62639</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>74566</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -214,7 +229,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1211035" y="6634842"/>
+          <a:off x="898071" y="6798127"/>
           <a:ext cx="13247961" cy="5658939"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -360,8 +375,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
@@ -390,28 +405,28 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="285750" y="12899572"/>
-          <a:ext cx="14124214" cy="6620799"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>462644</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>13608</xdr:rowOff>
+          <a:off x="285750" y="13280571"/>
+          <a:ext cx="14124214" cy="6239800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>122465</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
-      <xdr:colOff>156361</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>175875</xdr:rowOff>
+      <xdr:colOff>428504</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>135053</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -434,7 +449,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15158358" y="16587108"/>
+          <a:off x="15430501" y="14641286"/>
           <a:ext cx="8878539" cy="2448267"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -490,23 +505,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>435429</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>176893</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>353785</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>287439</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>82188</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B28A77A-7FF4-2647-B4AF-9F77CC5A3B40}"/>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>68034</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF49DB9C-2762-6204-8D01-C7CAD4AFB79E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -522,52 +537,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1660072" y="20179393"/>
-          <a:ext cx="12098438" cy="3905795"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>394607</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>326572</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF49DB9C-2762-6204-8D01-C7CAD4AFB79E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1006928" y="25146001"/>
-          <a:ext cx="12790715" cy="4803320"/>
+          <a:off x="966106" y="25309285"/>
+          <a:ext cx="12790715" cy="4667249"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -603,7 +574,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -622,23 +593,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>231321</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>353786</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{935CD693-0D2E-0654-6AED-CE7885A29C78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14927035" y="30616071"/>
+          <a:ext cx="9919608" cy="3129643"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>217715</xdr:colOff>
-      <xdr:row>158</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:colOff>285751</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>3040</xdr:colOff>
-      <xdr:row>177</xdr:row>
-      <xdr:rowOff>88959</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{943BF5F6-1E5F-A457-21B8-7C4B0E521C1D}"/>
+      <xdr:colOff>156813</xdr:colOff>
+      <xdr:row>205</xdr:row>
+      <xdr:rowOff>54960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A37A1C1-312A-592C-7EFA-35BE2D961B41}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -654,8 +669,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="830036" y="30139822"/>
-          <a:ext cx="12031754" cy="3667637"/>
+          <a:off x="898072" y="35296928"/>
+          <a:ext cx="12117491" cy="3810532"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -667,22 +682,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>244928</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:colOff>149679</xdr:colOff>
+      <xdr:row>186</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>367393</xdr:colOff>
-      <xdr:row>175</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{935CD693-0D2E-0654-6AED-CE7885A29C78}"/>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>217560</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>13993</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B84C688A-D14A-E15B-E3BA-A9804D229DE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -698,8 +713,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14940642" y="30207857"/>
-          <a:ext cx="9919608" cy="3129643"/>
+          <a:off x="14845393" y="35541857"/>
+          <a:ext cx="8640381" cy="2762636"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -711,22 +726,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>176894</xdr:colOff>
-      <xdr:row>182</xdr:row>
-      <xdr:rowOff>163285</xdr:rowOff>
+      <xdr:colOff>299358</xdr:colOff>
+      <xdr:row>208</xdr:row>
+      <xdr:rowOff>149680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>47956</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>163817</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A37A1C1-312A-592C-7EFA-35BE2D961B41}"/>
+      <xdr:colOff>198999</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>188477</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF9D2D63-EF86-5801-77B4-39995194C61C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -742,95 +757,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="789215" y="34834285"/>
-          <a:ext cx="12117491" cy="3810532"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>122465</xdr:colOff>
-      <xdr:row>183</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>190346</xdr:colOff>
-      <xdr:row>197</xdr:row>
-      <xdr:rowOff>122850</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B84C688A-D14A-E15B-E3BA-A9804D229DE1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14818179" y="34888714"/>
-          <a:ext cx="8640381" cy="2762636"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>340179</xdr:colOff>
-      <xdr:row>208</xdr:row>
-      <xdr:rowOff>54430</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>239820</xdr:colOff>
-      <xdr:row>234</xdr:row>
-      <xdr:rowOff>93227</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF9D2D63-EF86-5801-77B4-39995194C61C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="952500" y="39678430"/>
+          <a:off x="911679" y="39773680"/>
           <a:ext cx="12146070" cy="4991797"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -867,7 +794,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -911,7 +838,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1021,7 +948,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1065,7 +992,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1109,7 +1036,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1118,6 +1045,94 @@
         <a:xfrm>
           <a:off x="898071" y="66484500"/>
           <a:ext cx="16124465" cy="6681108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>503464</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>449036</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A9844F5-651D-2E94-8693-A5FD0CF099AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="503464" y="20383500"/>
+          <a:ext cx="14028965" cy="3946071"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>163288</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>149680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>598716</xdr:colOff>
+      <xdr:row>181</xdr:row>
+      <xdr:rowOff>27216</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EF99837-143C-C721-2111-146E0F2D98DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="775609" y="30629680"/>
+          <a:ext cx="13294178" cy="3878036"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1446,32 +1461,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D642923-020E-4F3D-A307-B18722D4CE25}">
-  <dimension ref="B32:Y239"/>
+  <dimension ref="A3:Y239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>0</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>1</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="182" spans="25:25" x14ac:dyDescent="0.25">
-      <c r="Y182" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="Y182" s="2"/>
     </row>
     <row r="207" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239" spans="3:3" ht="24" x14ac:dyDescent="0.4">
       <c r="C239" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1487,42 +1530,42 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -1536,28 +1579,28 @@
         <v>2000020</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1">
         <v>44774.353472222225</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
